--- a/老师要求跟踪-资料库表格.xlsx
+++ b/老师要求跟踪-资料库表格.xlsx
@@ -1514,14 +1514,44 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="n"/>
-      <c r="B25" s="3" t="n"/>
-      <c r="C25" s="3" t="n"/>
-      <c r="D25" s="4" t="n"/>
-      <c r="E25" s="7" t="n"/>
-      <c r="F25" s="7" t="n"/>
-      <c r="G25" s="3" t="n"/>
-      <c r="H25" s="3" t="n"/>
+      <c r="A25" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>平台沙箱 LFS/工具链可行性测试：试探平台沙箱是否执行 LFS 初始化（git lfs checkout）；确认主仓切换（MathPilot-lean-toolchain 为平台仓）后 main 合并必要性流程；尽快出可行性测试结论</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>验证/Mathlib</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-07T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="F25" s="7" t="inlineStr">
+        <is>
+          <t>待办</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>【部分完成】P2 主仓切换本地侧已闭环：lean 仓 root 形态一体化（代码全量 + Windows/Linux 双平台工具链同根 + mathlib closure-full + lsp-mcp wheels），lean_bridge root 形态探测链就位（Windows 仅认 .exe 防 ELF 误命中），Windows 真编译探针 exit=0；本地 commit 待 push，push 后走平台 T1/T2 阶梯测试验证沙箱行为</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>李老师9/7 平台问答</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n"/>
@@ -1783,7 +1813,7 @@
         </is>
       </c>
       <c r="B2" s="12">
-        <f>COUNTIF(老师要求跟踪!$F$2:$F$24,A2)</f>
+        <f>COUNTIF(老师要求跟踪!$F$2:$F$25,A2)</f>
         <v/>
       </c>
       <c r="C2" s="11" t="inlineStr">
@@ -1792,7 +1822,7 @@
         </is>
       </c>
       <c r="D2" s="12">
-        <f>COUNTIF(老师要求跟踪!$E$2:$E$24,C2)</f>
+        <f>COUNTIF(老师要求跟踪!$E$2:$E$25,C2)</f>
         <v/>
       </c>
     </row>
@@ -1803,7 +1833,7 @@
         </is>
       </c>
       <c r="B3" s="12">
-        <f>COUNTIF(老师要求跟踪!$F$2:$F$24,A3)</f>
+        <f>COUNTIF(老师要求跟踪!$F$2:$F$25,A3)</f>
         <v/>
       </c>
       <c r="C3" s="11" t="inlineStr">
@@ -1812,7 +1842,7 @@
         </is>
       </c>
       <c r="D3" s="12">
-        <f>COUNTIF(老师要求跟踪!$E$2:$E$24,C3)</f>
+        <f>COUNTIF(老师要求跟踪!$E$2:$E$25,C3)</f>
         <v/>
       </c>
     </row>
@@ -1823,7 +1853,7 @@
         </is>
       </c>
       <c r="B4" s="12">
-        <f>COUNTIF(老师要求跟踪!$F$2:$F$24,A4)</f>
+        <f>COUNTIF(老师要求跟踪!$F$2:$F$25,A4)</f>
         <v/>
       </c>
       <c r="C4" s="11" t="inlineStr">
@@ -1832,7 +1862,7 @@
         </is>
       </c>
       <c r="D4" s="12">
-        <f>COUNTIF(老师要求跟踪!$E$2:$E$24,C4)</f>
+        <f>COUNTIF(老师要求跟踪!$E$2:$E$25,C4)</f>
         <v/>
       </c>
     </row>
@@ -1876,7 +1906,7 @@
         </is>
       </c>
       <c r="B8" s="12">
-        <f>COUNTIF(老师要求跟踪!$C$2:$C$24,A8)</f>
+        <f>COUNTIF(老师要求跟踪!$C$2:$C$25,A8)</f>
         <v/>
       </c>
     </row>
@@ -1887,7 +1917,7 @@
         </is>
       </c>
       <c r="B9" s="12">
-        <f>COUNTIF(老师要求跟踪!$C$2:$C$24,A9)</f>
+        <f>COUNTIF(老师要求跟踪!$C$2:$C$25,A9)</f>
         <v/>
       </c>
     </row>
@@ -1898,7 +1928,7 @@
         </is>
       </c>
       <c r="B10" s="12">
-        <f>COUNTIF(老师要求跟踪!$C$2:$C$24,A10)</f>
+        <f>COUNTIF(老师要求跟踪!$C$2:$C$25,A10)</f>
         <v/>
       </c>
     </row>
@@ -1909,7 +1939,7 @@
         </is>
       </c>
       <c r="B11" s="12">
-        <f>COUNTIF(老师要求跟踪!$C$2:$C$24,A11)</f>
+        <f>COUNTIF(老师要求跟踪!$C$2:$C$25,A11)</f>
         <v/>
       </c>
     </row>
@@ -1920,7 +1950,7 @@
         </is>
       </c>
       <c r="B12" s="12">
-        <f>COUNTIF(老师要求跟踪!$C$2:$C$24,A12)</f>
+        <f>COUNTIF(老师要求跟踪!$C$2:$C$25,A12)</f>
         <v/>
       </c>
     </row>
@@ -1931,7 +1961,7 @@
         </is>
       </c>
       <c r="B13" s="12">
-        <f>COUNTIF(老师要求跟踪!$C$2:$C$23,A13)</f>
+        <f>COUNTIF(老师要求跟踪!$C$2:$C$25,A13)</f>
         <v/>
       </c>
     </row>
@@ -1942,7 +1972,7 @@
         </is>
       </c>
       <c r="B14" s="12">
-        <f>COUNTIF(老师要求跟踪!$C$2:$C$23,A14)</f>
+        <f>COUNTIF(老师要求跟踪!$C$2:$C$25,A14)</f>
         <v/>
       </c>
     </row>
@@ -1953,7 +1983,7 @@
         </is>
       </c>
       <c r="B15" s="12">
-        <f>COUNTIF(老师要求跟踪!$C$2:$C$23,A15)</f>
+        <f>COUNTIF(老师要求跟踪!$C$2:$C$25,A15)</f>
         <v/>
       </c>
     </row>
@@ -1968,6 +1998,7 @@
         <v/>
       </c>
     </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
@@ -1987,7 +2018,7 @@
         </is>
       </c>
       <c r="B19" s="12">
-        <f>COUNTIF(老师要求跟踪!$A$2:$A$23,"&gt;=26")</f>
+        <f>COUNTIF(老师要求跟踪!$A$2:$A$25,"&gt;=26")</f>
         <v/>
       </c>
     </row>
